--- a/Yael_Siso_System_Info.xlsx
+++ b/Yael_Siso_System_Info.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לפני פגישה" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="בקרת איכות" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תהליך גבייה" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פרויקט תקציב 1500" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -665,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.83203125" customWidth="1" min="1" max="1"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>שלב מסתיים → גבייה עוברת ל-Current אוטומטית</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>תעריף שעתי פר פרויקט (לא גלובלי)</t>
+          <t>יצירת יוזרים לבנות הצוות (9 team users)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1071,7 +1076,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>כבר היה מוכן בקוד</t>
+          <t>מוקם, ממתין לאישור יעל על מסך team</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1091,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gmail API — מסלול 2</t>
+          <t>Gmail API מחובר 03/05</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1131,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>לינקים ל-Drive ב-Knowledge + Client Card</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1191,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>לא יבוצע</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>פרויקט נפרד</t>
+          <t>יקר (3,000 ש"ח), יעל ויתרה</t>
         </is>
       </c>
     </row>
@@ -1207,6 +1217,106 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>team נכנסות ישר ל-Projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>אישור יעל למסך team לפני שליחת פרטים לבנות</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>יוזרים מוכנים, לא נשלחו פרטים</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>מודול ניהול תקציב לקוח (1,500 ש"ח)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>מאושר</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7 פיצ׳רים, בלי פורטל לקוח. פירוט בשיט נפרד</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>הרצת SQL להקמת טבלאות תקציב</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>טליה מריצה ב-Supabase SQL Editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>מייל גבייה דרך Gmail API (במקום mailto)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Client Billing + Supplier Billing — מודאל + Gmail API</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>בדיקת מיילים: מדריכי הדרכה + מיילים ספקים/לקוחות</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>לבדוק אחרי רענון cache — Ctrl+Shift+R</t>
         </is>
       </c>
     </row>
@@ -1961,4 +2071,254 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>פרויקט: מודול ניהול תקציב לקוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>תקציב:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1,500 ש"ח</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>סטטוס:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>מאושר ע"י יעל</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>פיצ׳ר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>סטטוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>טאב Budget בפרויקט</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>טבלה עם שורות: נושא, ספק, סכום, מע"מ אוטומטי, סטטוס</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>סיכום חי</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>סה"כ מתוכנן / שולם / נשאר + בר התקדמות</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>רישום תשלום</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>כפתור על שורה: תאריך + סכום + הערה, סטטוס מתעדכן אוטומטית</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>בקשת תשלום במייל</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>מודאל תצוגה מקדימה, שליחה מ-hello@yaelsiso.com, פרטי בנק נשלפים אוטומטית</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>פרטי בנק על ספקים</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>שדות בכרטיס ספק: שם חשבון, בנק, סניף, מספר חשבון</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ייבוא מאקסל</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ייבוא BITTON BUDGET כדוגמה ראשונה</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>לינק לתיקיית Drive</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>שדה לינק לתיקיית חשבוניות ב-Google Drive (לא העלאה פנימית)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>מה לא נכלל:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>העלאת חשבוניות פנימית</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>חשבוניות נשמרות ב-Drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>מייל סיכום חודשי אוטומטי</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>קלואי שולחת ידנית</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>פורטל לקוח</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>יקר (3,000 ש"ח)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Yael_Siso_System_Info.xlsx
+++ b/Yael_Siso_System_Info.xlsx
@@ -704,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.83203125" customWidth="1" min="1" max="1"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>מאושר</t>
+          <t>בוצע</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7 פיצ׳רים, בלי פורטל לקוח. פירוט בשיט נפרד</t>
+          <t>מודול תקציב מלא + ייבוא אקסל + פרטי בנק + מיילים</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ממתין</t>
+          <t>בוצע</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>טליה מריצה ב-Supabase SQL Editor</t>
+          <t>SQL רץ בהצלחה</t>
         </is>
       </c>
     </row>
@@ -1317,6 +1317,150 @@
       <c r="D34" t="inlineStr">
         <is>
           <t>לבדוק אחרי רענון cache — Ctrl+Shift+R</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>קישור אבני דרך לגבייה — ממתין לאישור קלואי</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>billing_mapping_for_chloe.xlsx נשלח. קלואי מאשרת קישורים + start/end. ישפיע על הקוד</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>יומן עבודה — שם אוטומטי + תצוגה אישית ל-Team</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>גבייה — שלב Pending Approval לפני Current</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>גבייה — סטטוס ניתן לשינוי ידני בכל שורה</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>גבייה — תצוגת מע"מ בשליחה ללקוח</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>לוגו חדש — ממתין לקלואי</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>קלואי שולחת</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>נוסחי מיילים — לעבור עם קלואי</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>email_templates_all.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>תמחורי תכולות — אחרי יפן</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ממתין</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>יעל</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2295,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2315,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2335,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2355,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2375,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2395,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2415,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
     </row>
